--- a/03_Outputs/all/01_TablasDescriptivas/idx14_seguridad_summary_labels.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx14_seguridad_summary_labels.xlsx
@@ -436,7 +436,7 @@
         <v>-0.02007781115204312</v>
       </c>
       <c r="E3">
-        <v>0.0235244202985534</v>
+        <v>0.02352442029855342</v>
       </c>
       <c r="F3">
         <v>-0.135940409683426</v>
